--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:44</t>
+    <t xml:space="preserve">2026-09-09 23:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:44</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:32</t>
+    <t xml:space="preserve">2026-09-23 13:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:04</t>
+    <t xml:space="preserve">2026-10-02 14:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Tomé</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Talcahuano</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:53</t>
+    <t xml:space="preserve">2026-10-04 09:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:50</t>
+    <t xml:space="preserve">2026-10-05 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -716,7 +716,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>71899.62</v>
+        <v>71899.63</v>
       </c>
     </row>
     <row r="11">
